--- a/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pia est à la librairie avec maman. Elle voit un petit livre. Elle a envie. L'argent se range. Pia ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte. Pia dit : s'il te plaît, ce livre ? Maman écoute. Elle dit oui. Elle paie. Pia dit merci. On demande à l'adulte.</t>
+          <t>Pia est à la librairie avec maman. Elle voit un petit livre. Elle a envie. L'argent se range. Pia ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte. S'il te plaît, ce livre ? Maman écoute. Elle dit oui. Elle paie. Pia dit merci. On demande à l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Pia est à la librairie avec maman. Elle voit un petit livre. Elle a envie. L'argent se range. Pia ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte.
+enfant-f|S'il te plaît, ce livre ? Maman écoute. Elle dit oui. Elle paie.
+narrateur|Pia dit merci. On demande à l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Pia veut un livre. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Pia a demandé à l'adulte. Maman a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Elles sortent. Pia tient le livre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Pia dit merci. On demande à l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Pia veut un livre. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Pia a demandé à l'adulte. Maman a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Elles sortent. Pia tient le livre.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pia demande pour un livre</t>
+          <t>Le livre d'images de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut un livre d'images. Le premier rayon n'en a pas. Au second, elle tire un livre. Maman attend. Nina demande. Le livre est à elle.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pia est à la librairie avec maman. Elle voit un petit livre. Elle a envie. L'argent se range. Pia ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte. S'il te plaît, ce livre ? Maman écoute. Elle dit oui. Elle paie. Pia dit merci. On demande à l'adulte.</t>
+          <t>Deux allées sentent le papier neuf. Le bois des rayons est sombre, lisse. Une poussière d'or flotte dans le jour. Maman pousse la porte vitrée. Un tapis étouffe les pas. Une lampe basse éclaire le comptoir. Ça sent le papier. Oui. On cherche un livre d'images. Nina glisse la main sur un dos. En ce moment, Nina entre dans la première allée. Les dos sont épais, sans images. Il n'y en a pas. C'est l'autre rayon. Tu viens ? Elles tournent au bout. La seconde allée est plus basse. Des couvertures colorées regardent. Nina s'arrête. Un petit livre montre un bateau. Celui-là. Il a un bateau. Nina tire le livre. Le papier racle le bois. Maman ne sort pas l'argent. Nina. Tu me demandes ? Le livre reste à moitié sorti. Oh. Nina rentre le livre d'un doigt. On achète si tu demandes. Tu te souviens ? Je peux demander. Tu me dis s'il te plaît ? Oui, maman. Le bateau du livre attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pia est à la librairie avec maman. Elle voit un petit livre. Elle a envie. L'argent se range. Pia ne le prend pas. Elle va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt; à maman. Maman, c'est l'adulte. Pia dit : s'il te plaît, ce livre ? Maman écoute. Elle dit oui. Elle paie. Pia dit merci. On demande à l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Deux allées sentent le papier neuf. Le bois des rayons est sombre, lisse. Une poussière d'or flotte dans le jour. Maman pousse la porte vitrée. Un tapis étouffe les pas. Une lampe basse éclaire le comptoir. Ça sent le papier. Oui. On cherche un livre d'images. Nina glisse la main sur un dos. En ce moment, Nina entre dans la première allée. Les dos sont épais, sans images. Il n'y en a pas. C'est l'autre rayon. Tu viens ? Elles tournent au bout. La seconde allée est plus basse. Des couvertures colorées regardent. Nina s'arrête. Un petit livre montre un bateau. Celui-là. Il a un bateau. Nina tire le livre. Le papier racle le bois. Maman ne sort pas l'argent. Nina. Tu me demandes ? Le livre reste à moitié sorti. Oh. Nina rentre le livre d'un doigt. On achète si tu demandes. Tu te souviens ? Je peux demander. Tu me dis s'il te plaît ? Oui, maman. Le bateau du livre attend encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,44 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Pia est à la librairie avec maman. Elle voit un petit livre. Elle a envie. L'argent se range. Pia ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte.
-enfant-f|S'il te plaît, ce livre ? Maman écoute. Elle dit oui. Elle paie.
-narrateur|Pia dit merci. On demande à l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Deux allées sentent le papier neuf.
+narrateur|Le bois des rayons est sombre, lisse.
+narrateur|Une poussière d'or flotte dans le jour.
+narrateur|Maman pousse la porte vitrée.
+narrateur|Un tapis étouffe les pas.
+narrateur|Une lampe basse éclaire le comptoir.
+enfant-f|Ça sent le papier.
+maman|Oui.
+maman|On cherche un livre d'images.
+narrateur|Nina glisse la main sur un dos.
+narrateur|En ce moment, Nina entre dans la première allée.
+narrateur|Les dos sont épais, sans images.
+enfant-f|Il n'y en a pas.
+maman|C'est l'autre rayon.
+maman|Tu viens ?
+narrateur|Elles tournent au bout.
+narrateur|La seconde allée est plus basse.
+narrateur|Des couvertures colorées regardent.
+narrateur|Nina s'arrête.
+narrateur|Un petit livre montre un bateau.
+enfant-f|Celui-là.
+enfant-f|Il a un bateau.
+narrateur|Nina tire le livre.
+narrateur|Le papier racle le bois.
+narrateur|Maman ne sort pas l'argent.
+maman|Nina.
+maman|Tu me demandes ?
+narrateur|Le livre reste à moitié sorti.
+enfant-f|Oh.
+narrateur|Nina rentre le livre d'un doigt.
+maman|On achète si tu demandes.
+maman|Tu te souviens ?
+enfant-f|Je peux demander.
+maman|Tu me dis s'il te plaît ?
+enfant-f|Oui, maman.
+narrateur|Le bateau du livre attend encore.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,19 +1386,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Nina veut le livre d'images. Que fait-elle ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Nina veut le livre d'images. Que fait-elle ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Pia veut un livre. Que fait-elle ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pia veut un livre. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Pia veut un livre. Que fait-elle ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>demander</t>
@@ -1362,7 +1406,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | maman | l'adulte</t>
+          <t>demander | elle demande | à maman | s'il te plaît</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1377,7 +1421,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>L'argent se range. Elle le dit à qui ?</t>
+          <t>Elle demande à maman. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1419,14 +1463,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1498,10 +1542,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Pia veut un livre. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina veut le livre d'images.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,12 +1570,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Pia a demandé à l'adulte. Maman a écouté.</t>
+          <t>Maman, s'il te plaît. Je peux avoir ce livre ? Oui. Merci, Nina. Tu as demandé. Maman ouvre le petit sac. Elle pose l'argent sur le comptoir. On glisse le livre dans un sachet. Nina le prend contre elle. Le sachet est lisse, un peu froid. Il est à moi. Oui. Parce que tu as demandé. Tu le tiens bien ? Oui, maman. Elles quittent la seconde allée. Le tapis étouffe encore les pas. Nina sent le sachet contre sa veste.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pia a demandé à l'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt;. Maman a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman, s'il te plaît. Je peux avoir ce livre ? Oui. Merci, Nina. Tu as demandé. Maman ouvre le petit sac. Elle pose l'argent sur le comptoir. On glisse le livre dans un sachet. Nina le prend contre elle. Le sachet est lisse, un peu froid. Il est à moi. Oui. Parce que tu as demandé. Tu le tiens bien ? Oui, maman. Elles quittent la seconde allée. Le tapis étouffe encore les pas. Nina sent le sachet contre sa veste.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,7 +1638,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1670,10 +1714,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Pia a demandé à l'adulte. Maman a écouté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-f|Maman, s'il te plaît.
+enfant-f|Je peux avoir ce livre ?
+maman|Oui.
+maman|Merci, Nina.
+maman|Tu as demandé.
+narrateur|Maman ouvre le petit sac.
+narrateur|Elle pose l'argent sur le comptoir.
+narrateur|On glisse le livre dans un sachet.
+narrateur|Nina le prend contre elle.
+narrateur|Le sachet est lisse, un peu froid.
+enfant-f|Il est à moi.
+maman|Oui.
+maman|Parce que tu as demandé.
+maman|Tu le tiens bien ?
+enfant-f|Oui, maman.
+narrateur|Elles quittent la seconde allée.
+narrateur|Le tapis étouffe encore les pas.
+narrateur|Nina sent le sachet contre sa veste.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,12 +1758,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Elles sortent. Pia tient le livre.</t>
+          <t>Dehors, le jour est plus vif. Nina marche avec le sachet. Le bateau de la couverture se sent. On le regardera à la maison ? Oui. Le bateau. Tu as demandé avant d'acheter. Bravo. Une feuille tourne près du caniveau. Le sachet tape un peu la jambe. Nina serre le livre contre elle. Le papier sent encore la boutique.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Elles sortent. Pia tient le livre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dehors, le jour est plus vif. Nina marche avec le sachet. Le bateau de la couverture se sent. On le regardera à la maison ? Oui. Le bateau. Tu as demandé avant d'acheter. Bravo. Une feuille tourne près du caniveau. Le sachet tape un peu la jambe. Nina serre le livre contre elle. Le papier sent encore la boutique.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1766,7 +1826,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1834,10 +1894,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Elles sortent. Pia tient le livre.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Dehors, le jour est plus vif.
+narrateur|Nina marche avec le sachet.
+narrateur|Le bateau de la couverture se sent.
+maman|On le regardera à la maison ?
+enfant-f|Oui.
+enfant-f|Le bateau.
+maman|Tu as demandé avant d'acheter.
+maman|Bravo.
+narrateur|Une feuille tourne près du caniveau.
+narrateur|Le sachet tape un peu la jambe.
+narrateur|Nina serre le livre contre elle.
+narrateur|Le papier sent encore la boutique.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,12 +1932,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>À la maison, Nina s'assoit. Elle sort le livre du sachet. Elle ouvre la première page. Le bateau a une voile rouge. Il avance. Oui. Tu l'as dans les mains. Nina tourne la page, tout doux. Une vague dessinée mouille presque le papier. Elle est bleue. Comme la mer. Le livre d'images reste ouvert sur ses genoux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>À la maison, Nina s'assoit. Elle sort le livre du sachet. Elle ouvre la première page. Le bateau a une voile rouge. Il avance. Oui. Tu l'as dans les mains. Nina tourne la page, tout doux. Une vague dessinée mouille presque le papier. Elle est bleue. Comme la mer. Le livre d'images reste ouvert sur ses genoux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1930,7 +2000,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2002,10 +2072,20 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|À la maison, Nina s'assoit.
+narrateur|Elle sort le livre du sachet.
+narrateur|Elle ouvre la première page.
+narrateur|Le bateau a une voile rouge.
+enfant-f|Il avance.
+maman|Oui.
+maman|Tu l'as dans les mains.
+narrateur|Nina tourne la page, tout doux.
+narrateur|Une vague dessinée mouille presque le papier.
+enfant-f|Elle est bleue.
+maman|Comme la mer.
+narrateur|Le livre d'images reste ouvert sur ses genoux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>librairie</t>
+          <t>librairie, deux rayons de bois, odeur de papier</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pia, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
